--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8676542-60AB-1347-8E84-BA96B9DBCAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4582AA66-C4E3-4349-B5C2-3F3639E31CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="79">
   <si>
     <t>blank</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>Verschiedene Definitionen von Religion unterscheiden können, was sie umfassen und wofür sie nützlich sein können.</t>
+  </si>
+  <si>
+    <t>Rituale auf drei Ebenen (Formen, Funktionen, Bedeutungen) anhand von Beispielen schildern können.</t>
   </si>
 </sst>
 </file>
@@ -904,6 +907,9 @@
       <c r="M4" s="11" t="s">
         <v>66</v>
       </c>
+      <c r="N4" t="s">
+        <v>78</v>
+      </c>
       <c r="O4" t="str">
         <f t="shared" si="2"/>
         <v>[3]</v>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11027"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4582AA66-C4E3-4349-B5C2-3F3639E31CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2C62B5-1C9B-B741-8649-2D00193A524A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
   <si>
     <t>blank</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>Rituale auf drei Ebenen (Formen, Funktionen, Bedeutungen) anhand von Beispielen schildern können.</t>
+  </si>
+  <si>
+    <t>Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.</t>
   </si>
 </sst>
 </file>
@@ -962,6 +965,9 @@
       <c r="M5" s="9" t="s">
         <v>67</v>
       </c>
+      <c r="N5" t="s">
+        <v>79</v>
+      </c>
       <c r="O5" t="str">
         <f t="shared" si="2"/>
         <v>[4]</v>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2C62B5-1C9B-B741-8649-2D00193A524A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C9AC95-7998-124B-9654-9D9238F57B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C9AC95-7998-124B-9654-9D9238F57B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F659FDD-1C3E-634E-8C54-432E7BD9A994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
   <si>
     <t>blank</t>
   </si>
@@ -242,9 +242,6 @@
     <t>gemmekeMaraboutWomenDakar2009</t>
   </si>
   <si>
-    <t>bernerSynkretismus2001</t>
-  </si>
-  <si>
     <t>pelikanWrittenTorahTalmud2006</t>
   </si>
   <si>
@@ -273,6 +270,12 @@
   </si>
   <si>
     <t>Historische und gegenwärtige Beispiele der Gruppenbildung anhand eines differenzierten Konzepts von "Meister/Jüngerschaft" erläutern können.</t>
+  </si>
+  <si>
+    <t>Ebenen der Genderforschung erläutern können, auf die die Religionswissenschaft grundlegend eingehen kann.</t>
+  </si>
+  <si>
+    <t>schlieterReligionReligionswissenschaftUnd2012</t>
   </si>
 </sst>
 </file>
@@ -284,9 +287,16 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -354,18 +364,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -375,9 +385,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -851,7 +862,7 @@
         <v>63</v>
       </c>
       <c r="N3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" si="2"/>
@@ -911,7 +922,7 @@
         <v>66</v>
       </c>
       <c r="N4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="2"/>
@@ -966,7 +977,7 @@
         <v>67</v>
       </c>
       <c r="N5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" si="2"/>
@@ -1020,6 +1031,9 @@
       <c r="M6" s="9" t="s">
         <v>68</v>
       </c>
+      <c r="N6" t="s">
+        <v>79</v>
+      </c>
       <c r="O6" t="str">
         <f t="shared" si="2"/>
         <v>[5]</v>
@@ -1069,8 +1083,8 @@
         <f t="shared" si="4"/>
         <v>6-Orthodoxie</v>
       </c>
-      <c r="M7" s="9" t="s">
-        <v>69</v>
+      <c r="M7" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" si="2"/>
@@ -1172,7 +1186,7 @@
         <v>8-Schriften</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" si="2"/>
@@ -1224,7 +1238,7 @@
         <v>9-Objekte</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O10" t="str">
         <f t="shared" si="2"/>
@@ -1276,7 +1290,7 @@
         <v>10-Orte</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O11" t="str">
         <f t="shared" si="2"/>
@@ -1328,7 +1342,7 @@
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O12" t="str">
         <f t="shared" si="2"/>
@@ -1380,7 +1394,7 @@
         <v>12-Digitalisierung</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O13" t="str">
         <f t="shared" si="2"/>
@@ -1432,7 +1446,7 @@
         <v>13-Extremismus</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O14" t="str">
         <f t="shared" si="2"/>
@@ -1484,7 +1498,7 @@
         <v>14-Interreligiös</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F659FDD-1C3E-634E-8C54-432E7BD9A994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDA7E4F-0002-3E4B-A25B-BD7F522EB7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
   <si>
     <t>blank</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>schlieterReligionReligionswissenschaftUnd2012</t>
+  </si>
+  <si>
+    <t>Erklären können, wie Normativitätsansprüche in der Religionswissenschaft untersucht werden können.</t>
   </si>
 </sst>
 </file>
@@ -1086,6 +1089,9 @@
       <c r="M7" s="12" t="s">
         <v>80</v>
       </c>
+      <c r="N7" t="s">
+        <v>81</v>
+      </c>
       <c r="O7" t="str">
         <f t="shared" si="2"/>
         <v>[6]</v>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDA7E4F-0002-3E4B-A25B-BD7F522EB7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EC0469-4C45-094F-B07D-5C1BCA7B72D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="84">
   <si>
     <t>blank</t>
   </si>
@@ -279,6 +279,12 @@
   </si>
   <si>
     <t>Erklären können, wie Normativitätsansprüche in der Religionswissenschaft untersucht werden können.</t>
+  </si>
+  <si>
+    <t>Die mündliche und schriftliche Dynamik der abrahamitischen Religionen im Verhältnis zueinander zu beschreiben.</t>
+  </si>
+  <si>
+    <t>Leitfrage</t>
   </si>
 </sst>
 </file>
@@ -290,7 +296,7 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,6 +345,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -367,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -395,6 +408,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -701,7 +718,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -716,12 +733,12 @@
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="31.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="77.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5" customWidth="1"/>
+    <col min="14" max="15" width="77.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -765,13 +782,16 @@
         <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="3">
         <v>1</v>
       </c>
@@ -807,15 +827,15 @@
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Vorstellung</v>
       </c>
-      <c r="O2" t="str">
-        <f t="shared" ref="O2:O15" si="2">"["&amp;B2&amp;"]"</f>
+      <c r="P2" t="str">
+        <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
         <v>[1]</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <f>"---
 layout: post
 " &amp; B$1 &amp; ": " &amp; B2 &amp; "
-" &amp; O$1 &amp; ": " &amp; O2 &amp; "
+" &amp; P$1 &amp; ": " &amp; P2 &amp; "
 level: overview
 ---"</f>
         <v>---
@@ -826,7 +846,7 @@
 ---</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3">
         <v>2</v>
       </c>
@@ -867,15 +887,15 @@
       <c r="N3" t="s">
         <v>76</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <f t="shared" si="2"/>
         <v>[2]</v>
       </c>
-      <c r="P3" t="str">
-        <f t="shared" ref="P3:P15" si="5">"---
+      <c r="Q3" t="str">
+        <f>"---
 layout: post
 " &amp; B$1 &amp; ": " &amp; B3 &amp; "
-" &amp; O$1 &amp; ": " &amp; O3 &amp; "
+" &amp; P$1 &amp; ": " &amp; P3 &amp; "
 level: overview
 ---"</f>
         <v>---
@@ -886,7 +906,7 @@
 ---</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3">
         <v>3</v>
       </c>
@@ -927,12 +947,17 @@
       <c r="N4" t="s">
         <v>77</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <f t="shared" si="2"/>
         <v>[3]</v>
       </c>
-      <c r="P4" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q4" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B4 &amp; "
+" &amp; P$1 &amp; ": " &amp; P4 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 3
@@ -941,7 +966,7 @@
 ---</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>4</v>
       </c>
@@ -982,12 +1007,17 @@
       <c r="N5" t="s">
         <v>78</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <f t="shared" si="2"/>
         <v>[4]</v>
       </c>
-      <c r="P5" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q5" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B5 &amp; "
+" &amp; P$1 &amp; ": " &amp; P5 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 4
@@ -996,7 +1026,7 @@
 ---</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
         <v>5</v>
       </c>
@@ -1037,12 +1067,17 @@
       <c r="N6" t="s">
         <v>79</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <f t="shared" si="2"/>
         <v>[5]</v>
       </c>
-      <c r="P6" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q6" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B6 &amp; "
+" &amp; P$1 &amp; ": " &amp; P6 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 5
@@ -1051,7 +1086,7 @@
 ---</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
         <v>6</v>
       </c>
@@ -1092,12 +1127,17 @@
       <c r="N7" t="s">
         <v>81</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <f t="shared" si="2"/>
         <v>[6]</v>
       </c>
-      <c r="P7" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q7" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B7 &amp; "
+" &amp; P$1 &amp; ": " &amp; P7 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 6
@@ -1106,7 +1146,7 @@
 ---</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
         <v>7</v>
       </c>
@@ -1121,33 +1161,43 @@
         <v>18</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="3"/>
-        <v>7. Materialität und Körper: Kursbesuch: Kunst</v>
+        <v>7. Materialität und Körper: Wie werden heilige Schriften überliefert?</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="4"/>
-        <v>7-Kunst</v>
-      </c>
-      <c r="M8" s="9"/>
-      <c r="O8" t="str">
+        <v>7-Schriften</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N8" t="s">
+        <v>82</v>
+      </c>
+      <c r="P8" t="str">
         <f t="shared" si="2"/>
         <v>[7]</v>
       </c>
-      <c r="P8" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q8" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B8 &amp; "
+" &amp; P$1 &amp; ": " &amp; P8 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 7
@@ -1156,7 +1206,7 @@
 ---</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3">
         <v>8</v>
       </c>
@@ -1171,35 +1221,40 @@
         <v>18</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="3"/>
-        <v>8. Materialität und Körper: Wie werden heilige Schriften überliefert?</v>
+        <v>8. Materialität und Körper: Welche Rolle spielen materielle Objekte in der Religion?</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="K9" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="4"/>
-        <v>8-Schriften</v>
+        <v>8-Objekte</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O9" t="str">
+        <v>70</v>
+      </c>
+      <c r="P9" t="str">
         <f t="shared" si="2"/>
         <v>[8]</v>
       </c>
-      <c r="P9" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q9" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B9 &amp; "
+" &amp; P$1 &amp; ": " &amp; P9 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 8
@@ -1208,7 +1263,7 @@
 ---</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3">
         <v>9</v>
       </c>
@@ -1223,35 +1278,40 @@
         <v>18</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="3"/>
-        <v>9. Materialität und Körper: Welche Rolle spielen materielle Objekte in der Religion?</v>
+        <v>9. Materialität und Körper: Welche Rolle spielen heilige Orte in der Religion?</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L10" t="str">
         <f t="shared" si="4"/>
-        <v>9-Objekte</v>
+        <v>9-Orte</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="O10" t="str">
+        <v>71</v>
+      </c>
+      <c r="P10" t="str">
         <f t="shared" si="2"/>
         <v>[9]</v>
       </c>
-      <c r="P10" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q10" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B10 &amp; "
+" &amp; P$1 &amp; ": " &amp; P10 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 9
@@ -1260,7 +1320,7 @@
 ---</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3">
         <v>10</v>
       </c>
@@ -1274,36 +1334,39 @@
       <c r="E11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" t="s">
-        <v>44</v>
+      <c r="F11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="3"/>
-        <v>10. Materialität und Körper: Welche Rolle spielen heilige Orte in der Religion?</v>
+        <v>10. Materialität und Körper: Kursbesuch: Kunst</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K11" t="s">
-        <v>58</v>
+      <c r="K11" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="4"/>
-        <v>10-Orte</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O11" t="str">
+        <v>10-Kunst</v>
+      </c>
+      <c r="M11" s="9"/>
+      <c r="P11" t="str">
         <f t="shared" si="2"/>
         <v>[10]</v>
       </c>
-      <c r="P11" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q11" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B11 &amp; "
+" &amp; P$1 &amp; ": " &amp; P11 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 10
@@ -1312,7 +1375,7 @@
 ---</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3">
         <v>11</v>
       </c>
@@ -1350,12 +1413,17 @@
       <c r="M12" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <f t="shared" si="2"/>
         <v>[11]</v>
       </c>
-      <c r="P12" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q12" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B12 &amp; "
+" &amp; P$1 &amp; ": " &amp; P12 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 11
@@ -1364,7 +1432,7 @@
 ---</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3">
         <v>12</v>
       </c>
@@ -1402,12 +1470,17 @@
       <c r="M13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <f t="shared" si="2"/>
         <v>[12]</v>
       </c>
-      <c r="P13" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q13" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B13 &amp; "
+" &amp; P$1 &amp; ": " &amp; P13 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 12
@@ -1416,7 +1489,7 @@
 ---</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="5">
         <v>13</v>
       </c>
@@ -1454,12 +1527,17 @@
       <c r="M14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
         <f t="shared" si="2"/>
         <v>[13]</v>
       </c>
-      <c r="P14" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q14" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B14 &amp; "
+" &amp; P$1 &amp; ": " &amp; P14 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 13
@@ -1468,7 +1546,7 @@
 ---</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="5">
         <v>14</v>
       </c>
@@ -1506,12 +1584,17 @@
       <c r="M15" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
         <f t="shared" si="2"/>
         <v>[14]</v>
       </c>
-      <c r="P15" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q15" t="str">
+        <f>"---
+layout: post
+" &amp; B$1 &amp; ": " &amp; B15 &amp; "
+" &amp; P$1 &amp; ": " &amp; P15 &amp; "
+level: overview
+---"</f>
         <v>---
 layout: post
 session: 14
@@ -1520,7 +1603,7 @@
 ---</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="5">
         <v>15</v>
       </c>
@@ -1555,15 +1638,15 @@
         <f t="shared" si="4"/>
         <v>15-Abschluss</v>
       </c>
-      <c r="O16" t="str">
-        <f t="shared" ref="O16" si="6">"["&amp;B16&amp;"]"</f>
+      <c r="P16" t="str">
+        <f t="shared" ref="P16" si="5">"["&amp;B16&amp;"]"</f>
         <v>[15]</v>
       </c>
-      <c r="P16" t="str">
-        <f t="shared" ref="P16" si="7">"---
+      <c r="Q16" t="str">
+        <f>"---
 layout: post
 " &amp; B$1 &amp; ": " &amp; B16 &amp; "
-" &amp; O$1 &amp; ": " &amp; O16 &amp; "
+" &amp; P$1 &amp; ": " &amp; P16 &amp; "
 level: overview
 ---"</f>
         <v>---

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EC0469-4C45-094F-B07D-5C1BCA7B72D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A35DB5-3E34-A84B-8B69-0293B9ABA357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="85">
   <si>
     <t>blank</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>Leitfrage</t>
+  </si>
+  <si>
+    <t>Erklären können, wie die Forschung an materiellen Objekten den Glauben an das Transzendente greifbar macht.</t>
   </si>
 </sst>
 </file>
@@ -832,7 +835,7 @@
         <v>[1]</v>
       </c>
       <c r="Q2" t="str">
-        <f>"---
+        <f t="shared" ref="Q2:Q16" si="3">"---
 layout: post
 " &amp; B$1 &amp; ": " &amp; B2 &amp; "
 " &amp; P$1 &amp; ": " &amp; P2 &amp; "
@@ -867,7 +870,7 @@
         <v>36</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I16" si="3">B3 &amp; ". " &amp; E3 &amp; ": " &amp; G3</f>
+        <f t="shared" ref="I3:I16" si="4">B3 &amp; ". " &amp; E3 &amp; ": " &amp; G3</f>
         <v>2. Religion als Gegenstand: Was ist Religion?</v>
       </c>
       <c r="J3" s="3">
@@ -878,7 +881,7 @@
         <v>51</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" ref="L3:L16" si="4">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
+        <f t="shared" ref="L3:L16" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Definitionen</v>
       </c>
       <c r="M3" s="10" t="s">
@@ -892,12 +895,7 @@
         <v>[2]</v>
       </c>
       <c r="Q3" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B3 &amp; "
-" &amp; P$1 &amp; ": " &amp; P3 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 2
@@ -927,7 +925,7 @@
         <v>37</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3. Religion als Gegenstand: Was gilt als religiöses Ritual?</v>
       </c>
       <c r="J4" s="3">
@@ -938,7 +936,7 @@
         <v>52</v>
       </c>
       <c r="L4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3-Ritual</v>
       </c>
       <c r="M4" s="11" t="s">
@@ -952,12 +950,7 @@
         <v>[3]</v>
       </c>
       <c r="Q4" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B4 &amp; "
-" &amp; P$1 &amp; ": " &amp; P4 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 3
@@ -987,7 +980,7 @@
         <v>38</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4. Gruppen und Autorität: Wie bilden sich religiöse Gruppen und Autoritäten?</v>
       </c>
       <c r="J5" s="3">
@@ -998,7 +991,7 @@
         <v>53</v>
       </c>
       <c r="L5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4-Gruppen</v>
       </c>
       <c r="M5" s="9" t="s">
@@ -1012,12 +1005,7 @@
         <v>[4]</v>
       </c>
       <c r="Q5" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B5 &amp; "
-" &amp; P$1 &amp; ": " &amp; P5 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 4
@@ -1047,7 +1035,7 @@
         <v>39</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5. Gruppen und Autorität: Welche Rolle spielt Gender in der Religion?</v>
       </c>
       <c r="J6" s="3">
@@ -1058,7 +1046,7 @@
         <v>54</v>
       </c>
       <c r="L6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5-Gender</v>
       </c>
       <c r="M6" s="9" t="s">
@@ -1072,12 +1060,7 @@
         <v>[5]</v>
       </c>
       <c r="Q6" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B6 &amp; "
-" &amp; P$1 &amp; ": " &amp; P6 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 5
@@ -1107,7 +1090,7 @@
         <v>40</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6. Gruppen und Autorität: Wer oder was bestimmt die Orthodoxie?</v>
       </c>
       <c r="J7" s="3">
@@ -1118,7 +1101,7 @@
         <v>55</v>
       </c>
       <c r="L7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6-Orthodoxie</v>
       </c>
       <c r="M7" s="12" t="s">
@@ -1132,12 +1115,7 @@
         <v>[6]</v>
       </c>
       <c r="Q7" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B7 &amp; "
-" &amp; P$1 &amp; ": " &amp; P7 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 6
@@ -1167,7 +1145,7 @@
         <v>42</v>
       </c>
       <c r="I8" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7. Materialität und Körper: Wie werden heilige Schriften überliefert?</v>
       </c>
       <c r="J8" s="3">
@@ -1178,7 +1156,7 @@
         <v>57</v>
       </c>
       <c r="L8" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7-Schriften</v>
       </c>
       <c r="M8" s="9" t="s">
@@ -1192,12 +1170,7 @@
         <v>[7]</v>
       </c>
       <c r="Q8" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B8 &amp; "
-" &amp; P$1 &amp; ": " &amp; P8 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 7
@@ -1227,7 +1200,7 @@
         <v>43</v>
       </c>
       <c r="I9" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8. Materialität und Körper: Welche Rolle spielen materielle Objekte in der Religion?</v>
       </c>
       <c r="J9" s="3">
@@ -1238,23 +1211,21 @@
         <v>65</v>
       </c>
       <c r="L9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8-Objekte</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>70</v>
+      </c>
+      <c r="N9" t="s">
+        <v>84</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
         <v>[8]</v>
       </c>
       <c r="Q9" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B9 &amp; "
-" &amp; P$1 &amp; ": " &amp; P9 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 8
@@ -1284,7 +1255,7 @@
         <v>44</v>
       </c>
       <c r="I10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9. Materialität und Körper: Welche Rolle spielen heilige Orte in der Religion?</v>
       </c>
       <c r="J10" s="3">
@@ -1295,7 +1266,7 @@
         <v>58</v>
       </c>
       <c r="L10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9-Orte</v>
       </c>
       <c r="M10" s="9" t="s">
@@ -1306,12 +1277,7 @@
         <v>[9]</v>
       </c>
       <c r="Q10" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B10 &amp; "
-" &amp; P$1 &amp; ": " &amp; P10 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 9
@@ -1341,7 +1307,7 @@
         <v>41</v>
       </c>
       <c r="I11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10. Materialität und Körper: Kursbesuch: Kunst</v>
       </c>
       <c r="J11" s="3">
@@ -1352,7 +1318,7 @@
         <v>56</v>
       </c>
       <c r="L11" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10-Kunst</v>
       </c>
       <c r="M11" s="9"/>
@@ -1361,12 +1327,7 @@
         <v>[10]</v>
       </c>
       <c r="Q11" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B11 &amp; "
-" &amp; P$1 &amp; ": " &amp; P11 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 10
@@ -1396,7 +1357,7 @@
         <v>45</v>
       </c>
       <c r="I12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11. Materialität und Körper: Welche Wirkung hat die religiöse Praxis auf den Körper?</v>
       </c>
       <c r="J12" s="3">
@@ -1407,7 +1368,7 @@
         <v>64</v>
       </c>
       <c r="L12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
@@ -1418,12 +1379,7 @@
         <v>[11]</v>
       </c>
       <c r="Q12" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B12 &amp; "
-" &amp; P$1 &amp; ": " &amp; P12 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 11
@@ -1453,7 +1409,7 @@
         <v>46</v>
       </c>
       <c r="I13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12. Religionswissenschaft für heute: Wie wird Religion digital untersucht?</v>
       </c>
       <c r="J13" s="3">
@@ -1464,7 +1420,7 @@
         <v>59</v>
       </c>
       <c r="L13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12-Digitalisierung</v>
       </c>
       <c r="M13" s="9" t="s">
@@ -1475,12 +1431,7 @@
         <v>[12]</v>
       </c>
       <c r="Q13" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B13 &amp; "
-" &amp; P$1 &amp; ": " &amp; P13 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 12
@@ -1510,7 +1461,7 @@
         <v>47</v>
       </c>
       <c r="I14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13. Religionswissenschaft für heute: Wie sollte religiöser Extremismus verstanden werden?</v>
       </c>
       <c r="J14" s="3">
@@ -1521,7 +1472,7 @@
         <v>60</v>
       </c>
       <c r="L14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13-Extremismus</v>
       </c>
       <c r="M14" s="9" t="s">
@@ -1532,12 +1483,7 @@
         <v>[13]</v>
       </c>
       <c r="Q14" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B14 &amp; "
-" &amp; P$1 &amp; ": " &amp; P14 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 13
@@ -1567,7 +1513,7 @@
         <v>48</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14. Religionswissenschaft für heute: Sollten Religionswissenschaftler/innen am interreligiösen Dialog mitwirken?</v>
       </c>
       <c r="J15" s="5">
@@ -1578,7 +1524,7 @@
         <v>61</v>
       </c>
       <c r="L15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14-Interreligiös</v>
       </c>
       <c r="M15" s="9" t="s">
@@ -1589,12 +1535,7 @@
         <v>[14]</v>
       </c>
       <c r="Q15" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B15 &amp; "
-" &amp; P$1 &amp; ": " &amp; P15 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 14
@@ -1624,7 +1565,7 @@
         <v>49</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>15. Religionswissenschaft für heute: Wie gehe ich mit dem erworbenen Wissen um?</v>
       </c>
       <c r="J16" s="5">
@@ -1635,20 +1576,15 @@
         <v>62</v>
       </c>
       <c r="L16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15-Abschluss</v>
       </c>
       <c r="P16" t="str">
-        <f t="shared" ref="P16" si="5">"["&amp;B16&amp;"]"</f>
+        <f t="shared" ref="P16" si="6">"["&amp;B16&amp;"]"</f>
         <v>[15]</v>
       </c>
       <c r="Q16" t="str">
-        <f>"---
-layout: post
-" &amp; B$1 &amp; ": " &amp; B16 &amp; "
-" &amp; P$1 &amp; ": " &amp; P16 &amp; "
-level: overview
----"</f>
+        <f t="shared" si="3"/>
         <v>---
 layout: post
 session: 15

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A35DB5-3E34-A84B-8B69-0293B9ABA357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE27A9C-B375-EC44-8F31-69155BAD78D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="87">
   <si>
     <t>blank</t>
   </si>
@@ -288,6 +288,12 @@
   </si>
   <si>
     <t>Erklären können, wie die Forschung an materiellen Objekten den Glauben an das Transzendente greifbar macht.</t>
+  </si>
+  <si>
+    <t>Erklären können, auf welche Weise Orte sakrale Bedeutung erlangen, und diese Bedeutung anhand jüdischer, christlicher und islamischer Beispiele erläutern.</t>
+  </si>
+  <si>
+    <t>Was macht einen Ort für Pilger "heilig"?</t>
   </si>
 </sst>
 </file>
@@ -1272,6 +1278,12 @@
       <c r="M10" s="9" t="s">
         <v>71</v>
       </c>
+      <c r="N10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O10" t="s">
+        <v>86</v>
+      </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
         <v>[9]</v>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE27A9C-B375-EC44-8F31-69155BAD78D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5B0D6D-216F-6147-8985-C4F98E7DBC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="88">
   <si>
     <t>blank</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>Was macht einen Ort für Pilger "heilig"?</t>
+  </si>
+  <si>
+    <t>Die Gestaltung religiöser Kunst beobachten und beschreiben.</t>
   </si>
 </sst>
 </file>
@@ -1334,6 +1337,9 @@
         <v>10-Kunst</v>
       </c>
       <c r="M11" s="9"/>
+      <c r="N11" t="s">
+        <v>87</v>
+      </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
         <v>[10]</v>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5B0D6D-216F-6147-8985-C4F98E7DBC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8E81EE-08E4-BF47-BF40-309EFF66593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30240" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="90">
   <si>
     <t>blank</t>
   </si>
@@ -251,9 +251,6 @@
     <t>walker11Pilgrimage2018</t>
   </si>
   <si>
-    <t>csordasIntroduction1994</t>
-  </si>
-  <si>
     <t>campbellContextualizingCurrentDigital2020</t>
   </si>
   <si>
@@ -297,6 +294,15 @@
   </si>
   <si>
     <t>Die Gestaltung religiöser Kunst beobachten und beschreiben.</t>
+  </si>
+  <si>
+    <t>ladenhaufReligiositaetUndSpiritualitaet2010</t>
+  </si>
+  <si>
+    <t>Religionspsychologische Ansätze zur Krankheit und Heilung schildern.</t>
+  </si>
+  <si>
+    <t>Wie unterscheiden sich religiös-spirituelle Menschen von anderen im Krankheitsprozess?</t>
   </si>
 </sst>
 </file>
@@ -794,7 +800,7 @@
         <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>12</v>
@@ -897,7 +903,7 @@
         <v>63</v>
       </c>
       <c r="N3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
@@ -952,7 +958,7 @@
         <v>66</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1007,7 +1013,7 @@
         <v>67</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1062,7 +1068,7 @@
         <v>68</v>
       </c>
       <c r="N6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1114,10 +1120,10 @@
         <v>6-Orthodoxie</v>
       </c>
       <c r="M7" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N7" t="s">
         <v>80</v>
-      </c>
-      <c r="N7" t="s">
-        <v>81</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -1172,7 +1178,7 @@
         <v>69</v>
       </c>
       <c r="N8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1227,7 +1233,7 @@
         <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1282,10 +1288,10 @@
         <v>71</v>
       </c>
       <c r="N10" t="s">
+        <v>84</v>
+      </c>
+      <c r="O10" t="s">
         <v>85</v>
-      </c>
-      <c r="O10" t="s">
-        <v>86</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -1338,7 +1344,7 @@
       </c>
       <c r="M11" s="9"/>
       <c r="N11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -1390,7 +1396,13 @@
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>72</v>
+        <v>87</v>
+      </c>
+      <c r="N12" t="s">
+        <v>88</v>
+      </c>
+      <c r="O12" t="s">
+        <v>89</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -1442,7 +1454,7 @@
         <v>12-Digitalisierung</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -1494,7 +1506,7 @@
         <v>13-Extremismus</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -1546,7 +1558,7 @@
         <v>14-Interreligiös</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8E81EE-08E4-BF47-BF40-309EFF66593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6BC4AD-4C0A-C342-B64B-C733BC938884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30240" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>blank</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>Wie unterscheiden sich religiös-spirituelle Menschen von anderen im Krankheitsprozess?</t>
+  </si>
+  <si>
+    <t>Verständnis für die Aspekte religiöser Identität, Autorität und Gemeinschaft demonstrieren, die in digitalen Umgebungen untersucht werden könnten.</t>
+  </si>
+  <si>
+    <t>Wie verändern sich die Dynamiken religiöser Identität, Autorität und Gemeinschaft in digitalen Umgebungen? Inwiefern bleiben sie gleich?</t>
   </si>
 </sst>
 </file>
@@ -1456,6 +1462,12 @@
       <c r="M13" s="9" t="s">
         <v>72</v>
       </c>
+      <c r="N13" t="s">
+        <v>90</v>
+      </c>
+      <c r="O13" t="s">
+        <v>91</v>
+      </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
         <v>[12]</v>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10112"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6BC4AD-4C0A-C342-B64B-C733BC938884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509C38A0-501A-3E40-A2D9-F9A0D85A59EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -305,10 +305,10 @@
     <t>Wie unterscheiden sich religiös-spirituelle Menschen von anderen im Krankheitsprozess?</t>
   </si>
   <si>
-    <t>Verständnis für die Aspekte religiöser Identität, Autorität und Gemeinschaft demonstrieren, die in digitalen Umgebungen untersucht werden könnten.</t>
-  </si>
-  <si>
     <t>Wie verändern sich die Dynamiken religiöser Identität, Autorität und Gemeinschaft in digitalen Umgebungen? Inwiefern bleiben sie gleich?</t>
+  </si>
+  <si>
+    <t>Verständnis dafür zeigen, wie religiöse Identität, Gemeinschaft und Autorität in Online- und Offline-Umgebungen miteinander verwoben sind.</t>
   </si>
 </sst>
 </file>
@@ -1463,10 +1463,10 @@
         <v>72</v>
       </c>
       <c r="N13" t="s">
+        <v>91</v>
+      </c>
+      <c r="O13" t="s">
         <v>90</v>
-      </c>
-      <c r="O13" t="s">
-        <v>91</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509C38A0-501A-3E40-A2D9-F9A0D85A59EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49AB6AC-0B77-0A43-95FD-BE7EDC560C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,9 +158,6 @@
     <t>Wer oder was bestimmt die Orthodoxie?</t>
   </si>
   <si>
-    <t>Kursbesuch: Kunst</t>
-  </si>
-  <si>
     <t>Wie werden heilige Schriften überliefert?</t>
   </si>
   <si>
@@ -309,6 +306,9 @@
   </si>
   <si>
     <t>Verständnis dafür zeigen, wie religiöse Identität, Gemeinschaft und Autorität in Online- und Offline-Umgebungen miteinander verwoben sind.</t>
+  </si>
+  <si>
+    <t>Kursbesuch: Kunst (Shahid Alam)</t>
   </si>
 </sst>
 </file>
@@ -806,7 +806,7 @@
         <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>12</v>
@@ -845,7 +845,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
@@ -899,17 +899,17 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L16" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B3 &amp; ". " &amp; F3,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-Definitionen</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
@@ -954,17 +954,17 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
         <v>3-Ritual</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1009,17 +1009,17 @@
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
         <v>4-Gruppen</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1064,17 +1064,17 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>5-Gender</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1119,17 +1119,17 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L7" t="str">
         <f t="shared" si="5"/>
         <v>6-Orthodoxie</v>
       </c>
       <c r="M7" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" t="s">
         <v>79</v>
-      </c>
-      <c r="N7" t="s">
-        <v>80</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -1163,7 +1163,7 @@
         <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="4"/>
@@ -1174,17 +1174,17 @@
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="5"/>
         <v>7-Schriften</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1218,7 +1218,7 @@
         <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
@@ -1229,17 +1229,17 @@
         <v>8</v>
       </c>
       <c r="K9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
         <v>8-Objekte</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1273,7 +1273,7 @@
         <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
@@ -1284,20 +1284,20 @@
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L10" t="str">
         <f t="shared" si="5"/>
         <v>9-Orte</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N10" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" t="s">
         <v>84</v>
-      </c>
-      <c r="O10" t="s">
-        <v>85</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -1331,18 +1331,18 @@
         <v>26</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
-        <v>10. Materialität und Körper: Kursbesuch: Kunst</v>
+        <v>10. Materialität und Körper: Kursbesuch: Kunst (Shahid Alam)</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="M11" s="9"/>
       <c r="N11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -1384,7 +1384,7 @@
         <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="4"/>
@@ -1395,20 +1395,20 @@
         <v>11</v>
       </c>
       <c r="K12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="5"/>
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="N12" t="s">
         <v>87</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>88</v>
-      </c>
-      <c r="O12" t="s">
-        <v>89</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -1442,7 +1442,7 @@
         <v>31</v>
       </c>
       <c r="G13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
@@ -1453,20 +1453,20 @@
         <v>12</v>
       </c>
       <c r="K13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>12-Digitalisierung</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -1500,7 +1500,7 @@
         <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="4"/>
@@ -1511,14 +1511,14 @@
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
         <v>13-Extremismus</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -1552,7 +1552,7 @@
         <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="4"/>
@@ -1563,14 +1563,14 @@
         <v>14</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="5"/>
         <v>14-Interreligiös</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>
@@ -1604,7 +1604,7 @@
         <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" si="4"/>
@@ -1615,7 +1615,7 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L16" t="str">
         <f t="shared" si="5"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49AB6AC-0B77-0A43-95FD-BE7EDC560C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF6917D-FE72-9948-B358-2402830EFEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
   <si>
     <t>blank</t>
   </si>
@@ -251,9 +251,6 @@
     <t>campbellContextualizingCurrentDigital2020</t>
   </si>
   <si>
-    <t>riesebrodtFundamentalismusAlsPatriarchalische1990</t>
-  </si>
-  <si>
     <t>schmiedelInterreligioeserDialogAls2008</t>
   </si>
   <si>
@@ -309,6 +306,15 @@
   </si>
   <si>
     <t>Kursbesuch: Kunst (Shahid Alam)</t>
+  </si>
+  <si>
+    <t>Fundamentalismus, Radikalisierung und Extremismus definieren und Beispiele für jeden Begriff geben.</t>
+  </si>
+  <si>
+    <t>Wie definiert Riesebrodt den Fundamentalismus?</t>
+  </si>
+  <si>
+    <t>riesebrodt11FundamentalismusUnd1990</t>
   </si>
 </sst>
 </file>
@@ -320,9 +326,16 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -404,18 +417,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -425,17 +438,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,7 +820,7 @@
         <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>12</v>
@@ -909,7 +923,7 @@
         <v>62</v>
       </c>
       <c r="N3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P3" t="str">
         <f t="shared" si="2"/>
@@ -964,7 +978,7 @@
         <v>65</v>
       </c>
       <c r="N4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1019,7 +1033,7 @@
         <v>66</v>
       </c>
       <c r="N5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1074,7 +1088,7 @@
         <v>67</v>
       </c>
       <c r="N6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1126,10 +1140,10 @@
         <v>6-Orthodoxie</v>
       </c>
       <c r="M7" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" t="s">
         <v>78</v>
-      </c>
-      <c r="N7" t="s">
-        <v>79</v>
       </c>
       <c r="P7" t="str">
         <f t="shared" si="2"/>
@@ -1184,7 +1198,7 @@
         <v>68</v>
       </c>
       <c r="N8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1239,7 +1253,7 @@
         <v>69</v>
       </c>
       <c r="N9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1294,10 +1308,10 @@
         <v>70</v>
       </c>
       <c r="N10" t="s">
+        <v>82</v>
+      </c>
+      <c r="O10" t="s">
         <v>83</v>
-      </c>
-      <c r="O10" t="s">
-        <v>84</v>
       </c>
       <c r="P10" t="str">
         <f t="shared" si="2"/>
@@ -1331,7 +1345,7 @@
         <v>26</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
@@ -1350,7 +1364,7 @@
       </c>
       <c r="M11" s="9"/>
       <c r="N11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -1402,13 +1416,13 @@
         <v>11-Körper</v>
       </c>
       <c r="M12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="N12" t="s">
         <v>86</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>87</v>
-      </c>
-      <c r="O12" t="s">
-        <v>88</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -1463,10 +1477,10 @@
         <v>71</v>
       </c>
       <c r="N13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -1517,8 +1531,14 @@
         <f t="shared" si="5"/>
         <v>13-Extremismus</v>
       </c>
-      <c r="M14" s="9" t="s">
-        <v>72</v>
+      <c r="M14" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="N14" t="s">
+        <v>91</v>
+      </c>
+      <c r="O14" t="s">
+        <v>92</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -1570,7 +1590,7 @@
         <v>14-Interreligiös</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10119"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24rw/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF6917D-FE72-9948-B358-2402830EFEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817FFF95-573F-BD45-96BD-F527549A5640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30240" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="95">
   <si>
     <t>blank</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>riesebrodt11FundamentalismusUnd1990</t>
+  </si>
+  <si>
+    <t>Überlegen und erklären können, inwieweit religionswissenschaftliche Ansätze zum interreligiösen Dialog beitragen können, sollen und dürfen.</t>
   </si>
 </sst>
 </file>
@@ -1592,6 +1595,9 @@
       <c r="M15" s="9" t="s">
         <v>72</v>
       </c>
+      <c r="N15" t="s">
+        <v>94</v>
+      </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>
         <v>[14]</v>
